--- a/AAII_Financials/Quarterly/SCHL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCHL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
   <si>
     <t>SCHL</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E7" s="2">
         <v>46081</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45991</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45900</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45808</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45716</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45626</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45535</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45443</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45351</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45260</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45169</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45077</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44985</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44895</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44804</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44712</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44620</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44530</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44439</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44347</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44255</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44165</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44074</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43982</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43890</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43799</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43708</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43616</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43524</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43434</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43343</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43251</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43159</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43069</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42978</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42886</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42794</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42704</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>476100</v>
+      </c>
+      <c r="E8" s="3">
         <v>329100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>551100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>225600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>508300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>335400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>544600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>237200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>474900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>323700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>562600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>228500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>528300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>324900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>587900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>262900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>514400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>344500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>524200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>259800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>401400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>277500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>406200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>215200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>284000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>373300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>597200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>232600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>470700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>360100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>604700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>218400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>496200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>344700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>598300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>189200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>499600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>336200</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>623100</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>282700</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>190400</v>
+      </c>
+      <c r="E9" s="3">
         <v>150300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>225600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>123500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>207300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>154600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>228600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>128300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>192300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>148700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>234100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>130000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>220400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>161100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>260400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>144500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>224600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>169600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>238000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>133300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>198000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>146000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>199300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>123200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>166600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>183000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>264300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>137100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>215300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>176900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>262400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>125300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>209000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>166400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>253600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>115600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>213200</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>160300</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>271300</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>169700</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>285700</v>
+      </c>
+      <c r="E10" s="3">
         <v>178800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>325500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>102100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>301000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>180800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>316000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>108900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>282600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>175000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>328500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>98500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>307900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>163800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>327500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>118400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>289800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>174900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>286200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>126500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>203400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>131500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>206900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>92000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>117400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>190300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>332900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>95500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>255400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>183200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>342300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>93100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>287200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>178300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>344700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>73600</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>286400</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>175900</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>351800</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,98 +1496,101 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-119800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>8600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>8400</v>
       </c>
-      <c r="G14" s="3">
-        <v>10600</v>
-      </c>
       <c r="H14" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>9500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>500</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>6300</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-8300</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
         <v>400</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
         <v>200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>11900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>5300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>12000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>17800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>40000</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF14" s="3">
         <v>11500</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
@@ -1578,153 +1598,159 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>10100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>4300</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
       <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
         <v>6700</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>21700</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
-      </c>
       <c r="AO14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="3">
         <v>500</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E15" s="3">
         <v>12900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>16500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>16300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>17200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>16900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>16300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>15300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>15000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>14600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>14100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>13400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>13700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>13500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>13800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>13700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>13800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>13600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>14500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>14900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>14500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>14700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>15800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>15500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>15300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>16000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>15900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>15800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>14800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>13700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>14400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>13200</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>12000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>11500</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>10500</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>9900</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>10100</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>9500</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>9600</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>407700</v>
+      </c>
+      <c r="E17" s="3">
         <v>356300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>460000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>309700</v>
       </c>
-      <c r="G17" s="3">
-        <v>444500</v>
-      </c>
       <c r="H17" s="3">
+        <v>452600</v>
+      </c>
+      <c r="I17" s="3">
         <v>359200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>470100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>326000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>418400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>358400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>461500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>321600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>436200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>360800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>487800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>321000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>448900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>364000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>440800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>291800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>391700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>301700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>357400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>272200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>330200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>433300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>492100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>320000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>438700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>381500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>506500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>302200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>422300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>368400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>491100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>291000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>435400</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>359800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>511700</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>345800</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>68400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-27200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>91100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-84100</v>
       </c>
-      <c r="G18" s="3">
-        <v>63800</v>
-      </c>
       <c r="H18" s="3">
+        <v>55700</v>
+      </c>
+      <c r="I18" s="3">
         <v>-23800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>74500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-88800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>56500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-34700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>101100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-93100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>92100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-35900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>100100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-58100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>65500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-19500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>83400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-32000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>9700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-24200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>48800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-57000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-46200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-60000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>105100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-87400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>32000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-21400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>98200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-83800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>73900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-23700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>107200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-101800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>64200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>-23600</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>111400</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>-63100</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,19 +2085,20 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3">
         <v>1600</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>8</v>
@@ -2096,243 +2130,249 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-11800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>5700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>4500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>5200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-39600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-15500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>200</v>
       </c>
-      <c r="AM20" s="3">
-        <v>0</v>
-      </c>
       <c r="AN20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="3">
         <v>-300</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-400</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>81500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-14300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>106000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-67800</v>
       </c>
-      <c r="G21" s="3">
-        <v>81000</v>
-      </c>
       <c r="H21" s="3">
+        <v>72900</v>
+      </c>
+      <c r="I21" s="3">
         <v>-6900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>90800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-73500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>71500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-20100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>115200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-79700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>105800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-22400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>116900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-41700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>69600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-3700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>112300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-10100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>36200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>71000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-29100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-24900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-37300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>127600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-64500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>53200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>119000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-64200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>89100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-46100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>107600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-86100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>80500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>-8800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>126600</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>-48000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E22" s="3">
         <v>1900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>4800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>4700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>4900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>600</v>
-      </c>
-      <c r="L22" s="3">
-        <v>500</v>
       </c>
       <c r="M22" s="3">
         <v>500</v>
       </c>
       <c r="N22" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="O22" s="3">
         <v>300</v>
@@ -2340,8 +2380,8 @@
       <c r="P22" s="3">
         <v>300</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>8</v>
+      <c r="Q22" s="3">
+        <v>300</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>8</v>
@@ -2358,11 +2398,11 @@
       <c r="V22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X22" s="3">
         <v>6200</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>8</v>
@@ -2370,8 +2410,8 @@
       <c r="Z22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA22" s="3">
-        <v>100</v>
+      <c r="AA22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB22" s="3">
         <v>100</v>
@@ -2382,8 +2422,8 @@
       <c r="AD22" s="3">
         <v>100</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>8</v>
+      <c r="AE22" s="3">
+        <v>100</v>
       </c>
       <c r="AF22" s="3" t="s">
         <v>8</v>
@@ -2397,8 +2437,8 @@
       <c r="AI22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ22" s="3">
-        <v>0</v>
+      <c r="AJ22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK22" s="3">
         <v>0</v>
@@ -2406,8 +2446,8 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
-      <c r="AM22" s="3" t="s">
-        <v>8</v>
+      <c r="AM22" s="3">
+        <v>0</v>
       </c>
       <c r="AN22" s="3" t="s">
         <v>8</v>
@@ -2418,252 +2458,261 @@
       <c r="AP22" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ22" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E23" s="3">
         <v>91800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>75900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-97000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>48900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-28400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>70000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-91800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>47300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-34600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>101500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-98000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>95600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-26200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>100900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-57900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>53700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-19800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>89100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-33300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>8000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-22000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>47600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-51800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-47400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-60100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>104900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-87100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>31800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-20800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>98400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-83400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>71700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-63300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>91700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-101600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>64200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-23900</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>111000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>-63400</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E24" s="3">
         <v>29300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>20000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-25900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>33500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-24800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>21200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-29300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>11400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-8100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>24600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-23800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>19800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>25500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-12500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-4700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>20700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-8900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>12400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-34400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-16800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>33800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-28600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>13900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-8200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>26800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-22100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>23500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-22400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>34600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-37900</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>24600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-8400</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>43100</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>-23900</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E26" s="3">
         <v>62500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>55900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-71100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>15400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>48800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-62500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>35900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-26500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>76900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-74200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>75800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-19300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>75400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-45400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>52100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-15100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>68400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-24400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>7700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>35200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-39800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-43300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>71100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-58500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>17900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-12600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>71600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-61300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>48200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-40900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>57100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-63700</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>39600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-15500</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>67900</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>-39500</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E27" s="3">
         <v>62500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>55900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-71100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>15400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>48800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-62500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>35900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-26500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>76900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-74200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>75700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-19200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>74800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-45500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>52000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-15300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>68000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-24200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>7600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-13900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>35100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-39800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-43300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>71000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-58500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>17900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-12600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>71600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-61300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>48200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-40900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>57100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-63700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>39600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-15500</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>67900</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>-39500</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3230,17 +3291,17 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3" t="s">
+      <c r="AE29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -3248,32 +3309,35 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>2600</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-8300</v>
       </c>
-      <c r="AK29" s="3">
-        <v>0</v>
-      </c>
       <c r="AL29" s="3">
         <v>0</v>
       </c>
       <c r="AM29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="3">
         <v>-200</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>100</v>
       </c>
-      <c r="AO29" s="3">
-        <v>0</v>
-      </c>
       <c r="AP29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ29" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,19 +3583,22 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1600</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>8</v>
@@ -3560,208 +3630,214 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>-800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>11800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-5700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-4500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1100</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>39600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>15500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-200</v>
       </c>
-      <c r="AM32" s="3">
-        <v>0</v>
-      </c>
       <c r="AN32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="3">
         <v>300</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>400</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E33" s="3">
         <v>62500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>55900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-71100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>15400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>48800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-62500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>35900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-26500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>76900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-74200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>75700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-19200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>74800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-45500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>52000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-15300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>68000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-24200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>7600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-13900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>35100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-39800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-43300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>71000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-58500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>17900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-12600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>71600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-61300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>50800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-49200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>57100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-63700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>39400</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-15400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>67900</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>-39600</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E35" s="3">
         <v>62500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>55900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-71100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>15400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>48800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-62500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>35900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-26500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>76900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-74200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>75700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-19200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>74800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-45500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>52000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-15300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>68000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-24200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>7600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-13900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>35100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-39800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-43300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>71000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-58500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>17900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-12600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>71600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-61300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>50800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-49200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>57100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-63700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>39400</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-15400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>67900</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>-39600</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E38" s="2">
         <v>46081</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45991</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45900</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45808</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45716</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45626</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45535</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45443</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45351</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45260</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45169</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45077</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44985</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44895</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44804</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44712</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44620</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44530</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44439</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44347</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44255</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44165</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44074</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43982</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43890</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43799</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43708</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43616</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43524</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43434</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43343</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43251</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43159</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43069</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42978</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42886</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42794</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42704</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>134900</v>
+      </c>
+      <c r="E41" s="3">
         <v>104600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>99300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>94300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>124000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>94700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>139600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>84100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>113700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>110400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>149500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>125800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>224500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>198800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>261100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>239700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>316600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>308900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>300700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>308600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>366500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>353200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>356600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>355500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>393800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>263800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>277800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>199400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>334100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>338100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>358100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>269800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>391900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>362600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>387800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>311900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>444100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>461800</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>442900</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>287600</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4463,540 +4553,555 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>284100</v>
+      </c>
+      <c r="E43" s="3">
         <v>290600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>332700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>241300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>303200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>327300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>319000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>247200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>250200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>282900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>323400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>235300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>286900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>290200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>363300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>283300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>326200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>310600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>383100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>279700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>344900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>339300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>396600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>322800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>329800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>281200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>325100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>226100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>250100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>317300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>377300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>223700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>204900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>186000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>262400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>145400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>199200</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>172400</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>281600</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>222600</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>265000</v>
+      </c>
+      <c r="E44" s="3">
         <v>282500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>290700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>322200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>250200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>270800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>282000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>310300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>264200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>282500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>302300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>353200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>334500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>367500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>380400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>379100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>281400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>299400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>279300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>298100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>269700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>304800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>306500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>323200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>270600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>307700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>357800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>403600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>323700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>356800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>365600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>402300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>294900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>356900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>355700</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>386500</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>282500</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>351200</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>348300</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>375700</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E45" s="3">
         <v>3500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>354100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4400</v>
-      </c>
-      <c r="M45" s="3">
-        <v>5400</v>
       </c>
       <c r="N45" s="3">
         <v>5400</v>
       </c>
       <c r="O45" s="3">
+        <v>5400</v>
+      </c>
+      <c r="P45" s="3">
         <v>4700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>77500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>89400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>71800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>72400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>64400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>71700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>47200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>61000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>51400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>53700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>41100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>88500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>61900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>109700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>52700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>84800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>71300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>107600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>66600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>100100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>69200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>113000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>44700</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>69200</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>60200</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>721300</v>
+      </c>
+      <c r="E46" s="3">
         <v>735300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1134500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>730200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>725300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>757000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>811500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>715100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>676900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>728700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>840600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>784700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>892900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>927900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1082300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>991500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>996000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>991300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1027500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>958100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1028300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1058300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1111100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1055200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1035300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>941200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1022600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>938800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>960600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1097000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1172300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1003400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>958300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1005600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1075100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>956800</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>970500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1054600</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>1133000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>1009300</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E47" s="3">
         <v>40200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>39400</v>
-      </c>
-      <c r="F47" s="3">
-        <v>40000</v>
       </c>
       <c r="G47" s="3">
         <v>40000</v>
       </c>
       <c r="H47" s="3">
+        <v>40000</v>
+      </c>
+      <c r="I47" s="3">
         <v>38200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>38600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>39500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>37500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>36800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>38400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>38300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>37600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>37100</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>8</v>
@@ -5013,32 +5118,32 @@
       <c r="V47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W47" s="3">
+      <c r="W47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X47" s="3">
         <v>40300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>39800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>38500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>33900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>31000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>32400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>32000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>28500</v>
-      </c>
-      <c r="AE47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF47" s="3" t="s">
         <v>8</v>
@@ -5052,8 +5157,8 @@
       <c r="AI47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ47" s="3">
-        <v>0</v>
+      <c r="AJ47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK47" s="3">
         <v>0</v>
@@ -5073,252 +5178,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>492800</v>
+      </c>
+      <c r="E48" s="3">
         <v>457800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>275000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>610400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>620200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>615900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>623100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>630400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>611000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>604200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>620900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>619700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>607100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>585800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>586800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>590500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>598900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>590000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>603100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>622300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>635500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>638200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>657800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>669400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>672200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>650800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>654900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>661600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>577700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>574900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>571300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>563500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>555600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>530600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>514000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>487100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>475300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>455300</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>446100</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>438700</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>277300</v>
+      </c>
+      <c r="E49" s="3">
         <v>282000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>281800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>286300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>286800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>283400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>290800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>299100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>143100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>146800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>147300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>142200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>142600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>142300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>254300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>243300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>238400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>246000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>247600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>246600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>246300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>248700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>249000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>249600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>248000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>274400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>261800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>259400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>257200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>247500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>241500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>236700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>231500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>229300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>222400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>216100</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>215100</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>212900</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>207500</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>210500</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>149800</v>
+      </c>
+      <c r="E52" s="3">
         <v>169700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>166600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>204300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>183600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>196200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>201600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>204900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>115700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>123700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>110200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>111900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>102900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>109000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>110600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>106400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>107500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>113200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>102500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>98300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>57900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>50000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>50500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>48200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>47100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>49600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>60400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>56300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>83000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>103700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>96800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>96000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>80000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>68200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>96800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>99600</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>99500</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>124800</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>120900</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>116700</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1728100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1780800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1994400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1954600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1950100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1961300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2036800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1960000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1671200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1715200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1833500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1772300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1866700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1877500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2034000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1931700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1940800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1940500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1980700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1925300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2008300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2035000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2106900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2056300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2033600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1948400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2031700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1944600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1878500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2023100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2081900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1899600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1825400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1833700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1908300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1759600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>1760400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1847600</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>1907500</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>1775200</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,541 +6145,554 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>144200</v>
+      </c>
+      <c r="E57" s="3">
         <v>128500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>153600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>175800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>157300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>133500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>157200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>184000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>138500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>126100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>159500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>167700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>170900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>158400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>212400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>208900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>162300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>173400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>180500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>185600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>138000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>134300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>165500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>168300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>153600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>187900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>188900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>226400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>195300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>215300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>250300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>242300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>198900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>208400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>222100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>187200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>141200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>194200</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>216400</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>203600</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>52200</v>
+      </c>
+      <c r="E58" s="3">
         <v>53800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>47000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>47600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>53000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>50100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>40500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>51800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>30100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>54100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>29700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>28800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>29400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>27000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>6300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>13700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>14300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>89500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>182900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>190700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>19800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>19900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>10000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>11800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>15500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>14800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>7300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>11000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>13500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>15700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>7700</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>11300</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>12000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>6200</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>5800</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>7300</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>216100</v>
+      </c>
+      <c r="E59" s="3">
         <v>252500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>288000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>215800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>216900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>241100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>262400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>206700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>196100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>234800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>265200</v>
-      </c>
-      <c r="N59" s="3">
-        <v>217400</v>
       </c>
       <c r="O59" s="3">
         <v>217400</v>
       </c>
       <c r="P59" s="3">
+        <v>217400</v>
+      </c>
+      <c r="Q59" s="3">
         <v>249200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>507500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>453100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>450900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>472100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>476900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>386500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>374600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>405000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>421300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>375300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>337900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>430600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>446300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>384200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>338900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>469800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>475600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>373400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>239000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>283500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>305100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>251700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>239700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>308100</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>335700</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>265400</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>585500</v>
+      </c>
+      <c r="E60" s="3">
         <v>621100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>679500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>631400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>626400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>616700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>655800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>628400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>534700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>608500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>636700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>598700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>602300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>636900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>724700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>668300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>619700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>659200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>671700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>661600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>695500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>730000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>606600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>563500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>501500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>630300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>650700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>625400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>541500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>696100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>739400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>631400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>445800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>499600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>538500</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>450900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>387100</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>508100</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>559400</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>481100</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>367300</v>
+      </c>
+      <c r="E61" s="3">
         <v>262600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>353900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>410300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>346400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>359400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>348900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>329200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>93700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>79400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>84100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>83100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>78400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>62800</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -6566,32 +6709,32 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>7300</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>175000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>200000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>220100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>16400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>12400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>9300</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
@@ -6625,130 +6768,136 @@
       <c r="AP61" s="3">
         <v>0</v>
       </c>
+      <c r="AQ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E62" s="3">
         <v>22300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>26500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>31200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>15800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>38800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>40200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>38800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>23400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>24100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>25300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>27900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>91200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>97100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>102700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>96000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>99000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>114100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>123200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>128200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>137400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>145400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>131400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>102400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>107300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>113200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>64200</v>
-      </c>
-      <c r="AF62" s="3">
-        <v>57900</v>
       </c>
       <c r="AG62" s="3">
         <v>57900</v>
       </c>
       <c r="AH62" s="3">
-        <v>58800</v>
+        <v>57900</v>
       </c>
       <c r="AI62" s="3">
         <v>58800</v>
       </c>
       <c r="AJ62" s="3">
+        <v>58800</v>
+      </c>
+      <c r="AK62" s="3">
         <v>66500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>67100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>65700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>65400</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>70500</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>72900</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>977300</v>
+      </c>
+      <c r="E66" s="3">
         <v>908900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1063200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1076600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1003600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1020000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1050800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1002700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>653100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>717600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>754400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>717700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>702200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>727600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>817500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>766900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>723800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>756700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>771900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>777000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>827500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>859600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>920500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>910300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>854400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>750500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>771700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>749200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>607000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>754000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>797300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>690200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>504600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>566100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>605600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>516600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>452500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>578600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>632300</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>556600</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1037600</v>
+      </c>
+      <c r="E72" s="3">
         <v>1032100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>974200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>923500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>999700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>989500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>998700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>955600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1023700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>993500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1026000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>955100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1035600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>966400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>992400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>924100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>976500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>929500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>950100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>887000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>916400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>913900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>933100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>903100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>948000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>966200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1014700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>948900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1012600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1000500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1018400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>952100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1065200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1019600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1074100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1022200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1091200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1057100</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>1077700</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>1015000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>750800</v>
+      </c>
+      <c r="E76" s="3">
         <v>871900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>931200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>878000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>946500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>941300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>986000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>957300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1018100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>997600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1079100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1054600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1162900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1148400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1216500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1164800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1217000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1183800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1208800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1148300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1180800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1175400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1186400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1146000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1179200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1197900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1260000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1195400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1271500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1269100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1284600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1209400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1320800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1267600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1302700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1243000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1307900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>1269000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>1275200</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>1218600</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E80" s="2">
         <v>46081</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45991</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45900</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45808</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45716</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45626</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45535</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45443</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45351</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45260</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45169</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45077</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44985</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44895</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44804</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44712</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44620</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44530</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44439</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44347</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44255</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44165</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44074</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43982</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43890</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43799</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43708</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43616</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43524</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43434</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43343</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43251</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43159</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43069</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42978</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42886</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42794</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42704</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E81" s="3">
         <v>62500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>55900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-71100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>15400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>48800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-62500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>35900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-26500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>76900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-74200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>75700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-19200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>74800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-45500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>52000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-15300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>68000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-24200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>7600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-13900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>35100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-39800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-43300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>71000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-58500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>17900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-12600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>71600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-61300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>50800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-49200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>57100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-63700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>39400</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-15400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>67900</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>-39600</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E83" s="3">
         <v>17200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>16600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>15900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-14700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>15600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>15300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>-15300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>15500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>15400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>15700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>-14400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>15600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>16000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>16200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>15900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>16100</v>
-      </c>
-      <c r="U83" s="3">
-        <v>23200</v>
       </c>
       <c r="V83" s="3">
         <v>23200</v>
       </c>
       <c r="W83" s="3">
+        <v>23200</v>
+      </c>
+      <c r="X83" s="3">
         <v>22000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>22200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>23400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>22700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>22400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>22700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>22600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>22500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>21400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>20500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>20600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>19200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>17400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>17200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>15900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>15500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>16300</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>15100</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>15600</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>90000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-30500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>73200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-81800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>106900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-12000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>71200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-41900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>69900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>13100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>109700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-38100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>120000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>81600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-60300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>47500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>36900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>78000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>63600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>34500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>16400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>46100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-26000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-41900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>29700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>111900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-97600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>55900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>21000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>128500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-89000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>76600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>36500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>120800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-92400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>28000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>39200</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>179700</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-105500</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,83 +9910,84 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13400</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-10000</v>
       </c>
       <c r="F91" s="3">
         <v>-10000</v>
       </c>
       <c r="G91" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="H91" s="3">
         <v>-12300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-20000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-14600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-14700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-14800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-14300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-25200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-18900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-16200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-18200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-14500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-10100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-10900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
       <c r="AB91" s="3">
         <v>0</v>
       </c>
@@ -9774,46 +9995,49 @@
         <v>0</v>
       </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-24000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-19700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-23200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-28100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-29100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-38400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-21300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-32700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-37500</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-22600</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-15600</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-16900</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
         <v>435200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-14300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-14900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-20900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-14800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-200800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-20200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-20400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-27300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-21800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-34300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-19500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-29600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-16200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-12700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-13300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-14500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-15600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-10800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-15200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-8900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-21300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-26000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-24100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-24300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-43500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-31300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-35100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-37400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-45200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-47900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-30100</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-38800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-47200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-22600</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-10600</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-12400</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,118 +10455,119 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>5100</v>
+        <v>4600</v>
       </c>
       <c r="E96" s="3">
         <v>5100</v>
       </c>
       <c r="F96" s="3">
+        <v>5100</v>
+      </c>
+      <c r="G96" s="3">
         <v>5200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>5600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>5700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>5600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>5700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>5800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>6100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>6300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>6500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>6700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>6900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-6900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-5100</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-5200</v>
       </c>
       <c r="T96" s="3">
         <v>-5200</v>
       </c>
       <c r="U96" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="V96" s="3">
         <v>-5100</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-5200</v>
       </c>
       <c r="W96" s="3">
         <v>-5200</v>
       </c>
       <c r="X96" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-5200</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-5100</v>
       </c>
       <c r="AA96" s="3">
         <v>-5100</v>
       </c>
       <c r="AB96" s="3">
-        <v>-5200</v>
+        <v>-5100</v>
       </c>
       <c r="AC96" s="3">
         <v>-5200</v>
       </c>
       <c r="AD96" s="3">
-        <v>-5300</v>
+        <v>-5200</v>
       </c>
       <c r="AE96" s="3">
         <v>-5300</v>
       </c>
       <c r="AF96" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-5200</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-5400</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-5200</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-5300</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-5200</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-5300</v>
       </c>
       <c r="AL96" s="3">
         <v>-5300</v>
       </c>
       <c r="AM96" s="3">
-        <v>-5200</v>
+        <v>-5300</v>
       </c>
       <c r="AN96" s="3">
         <v>-5200</v>
@@ -10344,8 +10578,11 @@
       <c r="AP96" s="3">
         <v>-5200</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>-5200</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-59100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-400800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-52900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>66800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-60300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-16900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>211900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-46700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-31600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-58500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-39300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-60200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-50300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-30600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-26300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-15000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-82300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-105600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-6100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-30900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>193800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-17600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-9800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-12300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-15800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-9900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-5200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>5200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-14300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-14600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>1400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>2100</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-13400</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-200</v>
       </c>
       <c r="I101" s="3">
         <v>-200</v>
       </c>
       <c r="J101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K101" s="3">
         <v>500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-2000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-400</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-2000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>500</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-200</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>300</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>100</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>200</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-400</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E102" s="3">
         <v>5300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-29700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>29300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-44900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>55500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-29600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-39100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>23700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-98700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>25700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-62300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>21400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-76900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>7700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>8200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-7900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-57900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>13300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-38300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>130000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-14000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>78400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-134700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-20000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>88300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-122100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>29300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-25200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>75900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-132200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-17700</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>18900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>155300</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-112100</v>
       </c>
     </row>
